--- a/在宅評価シート.xlsx
+++ b/在宅評価シート.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\作業管理\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Relife-host-pc\nas\作業管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2B25B0-BCD6-4464-B67B-2800BF077AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="原紙 " sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'原紙 '!$A$1:$M$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'原紙 '!$A$1:$M$29</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -109,11 +110,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m/d;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,21 +139,7 @@
     </font>
     <font>
       <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -167,6 +154,32 @@
     <font>
       <sz val="18"/>
       <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -332,14 +345,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -354,16 +367,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -375,86 +385,95 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -735,74 +754,75 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultRowHeight="15.9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="5.21875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.21875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="8.88671875" style="1"/>
-    <col min="7" max="7" width="2.21875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.77734375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="3.77734375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="3.77734375" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="4.36328125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.1796875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="8.90625" style="1"/>
+    <col min="7" max="7" width="2.1796875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.81640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08984375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="3.81640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.54296875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="3.81640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
     </row>
     <row r="2" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-    </row>
-    <row r="3" spans="1:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+    </row>
+    <row r="3" spans="1:13" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="8"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
       <c r="E3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="I3" s="10" t="s">
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="9"/>
+      <c r="J3" s="3"/>
       <c r="K3" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
         <v>7</v>
       </c>
@@ -810,90 +830,90 @@
     <row r="4" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="33" t="s">
+    <row r="5" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-    </row>
-    <row r="6" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="33"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-    </row>
-    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+    </row>
+    <row r="6" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+    </row>
+    <row r="7" spans="1:13" ht="54.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>1</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="36"/>
-    </row>
-    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="32"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="34"/>
+    </row>
+    <row r="8" spans="1:13" ht="54.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>2</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="36"/>
-    </row>
-    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="32"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="34"/>
+    </row>
+    <row r="9" spans="1:13" ht="54.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>3</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="36"/>
-    </row>
-    <row r="10" spans="1:13" ht="31.8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="32"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="33"/>
+      <c r="M9" s="34"/>
+    </row>
+    <row r="10" spans="1:13" ht="31.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -907,312 +927,332 @@
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
     </row>
-    <row r="11" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="39" t="s">
+    <row r="11" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="38"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="16"/>
     </row>
     <row r="12" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>1</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
     </row>
     <row r="13" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>2</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
     </row>
     <row r="14" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>3</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-    </row>
-    <row r="15" spans="1:13" ht="31.2" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+    </row>
+    <row r="15" spans="1:13" ht="31.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="23"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="25"/>
     </row>
     <row r="17" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="26"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="28"/>
     </row>
     <row r="18" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="27"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
-      <c r="M18" s="29"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="31"/>
     </row>
     <row r="19" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="30"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="20"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="38"/>
     </row>
     <row r="20" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="11" t="s">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="13" t="s">
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M20" s="12"/>
+      <c r="M20" s="11"/>
     </row>
     <row r="21" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="20"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="38"/>
     </row>
     <row r="22" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="11" t="s">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="13" t="s">
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M22" s="12"/>
+      <c r="M22" s="11"/>
     </row>
     <row r="23" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="20"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="38"/>
     </row>
     <row r="24" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="11" t="s">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="13" t="s">
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M24" s="12"/>
+      <c r="M24" s="11"/>
     </row>
     <row r="25" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="30"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="20"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="37"/>
+      <c r="M25" s="38"/>
     </row>
     <row r="26" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="11" t="s">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="13" t="s">
+      <c r="J26" s="40"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M26" s="12"/>
+      <c r="M26" s="11"/>
     </row>
     <row r="27" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="20"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="37"/>
+      <c r="M27" s="38"/>
     </row>
     <row r="28" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="30"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="11" t="s">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="13" t="s">
+      <c r="J28" s="40"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M28" s="12"/>
+      <c r="M28" s="11"/>
     </row>
     <row r="29" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="31"/>
-      <c r="B29" s="31"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
     </row>
     <row r="30" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="31"/>
-      <c r="B30" s="31"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
     </row>
     <row r="31" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="31"/>
-      <c r="B31" s="31"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
     </row>
     <row r="32" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="31"/>
-      <c r="B32" s="31"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B13:M13"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C19:M19"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="A16:M18"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="C23:M23"/>
     <mergeCell ref="C25:M25"/>
     <mergeCell ref="C27:M27"/>
@@ -1224,35 +1264,15 @@
     <mergeCell ref="B12:M12"/>
     <mergeCell ref="I11:M11"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A21:B22"/>
     <mergeCell ref="C21:M21"/>
     <mergeCell ref="J20:K20"/>
     <mergeCell ref="C20:H20"/>
     <mergeCell ref="C22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="B13:M13"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C19:M19"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="A16:M18"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="J28:K28"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"2025年,2026年,2027年"</formula1>
     </dataValidation>
   </dataValidations>

--- a/在宅評価シート.xlsx
+++ b/在宅評価シート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Relife-host-pc\nas\作業管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2B25B0-BCD6-4464-B67B-2800BF077AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4797C8-5343-44F7-9853-4D86300B0E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -385,11 +385,80 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -403,77 +472,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -774,42 +774,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
     </row>
     <row r="3" spans="1:13" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
       <c r="E3" s="2" t="s">
         <v>1</v>
       </c>
@@ -831,87 +831,87 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
     </row>
     <row r="6" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
     </row>
     <row r="7" spans="1:13" ht="54.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>1</v>
       </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="34"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="37"/>
     </row>
     <row r="8" spans="1:13" ht="54.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>2</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="34"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="37"/>
     </row>
     <row r="9" spans="1:13" ht="54.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>3</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="34"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="37"/>
     </row>
     <row r="10" spans="1:13" ht="31.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="6"/>
@@ -928,331 +928,311 @@
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="39" t="s">
+      <c r="H11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="16"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="39"/>
     </row>
     <row r="12" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>1</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
     </row>
     <row r="13" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>2</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
     </row>
     <row r="14" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>3</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
     </row>
     <row r="15" spans="1:13" ht="31.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="25"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="24"/>
     </row>
     <row r="17" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="28"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="27"/>
     </row>
     <row r="18" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="29"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="31"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="30"/>
     </row>
     <row r="19" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="38"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="21"/>
     </row>
     <row r="20" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
       <c r="I20" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
       <c r="L20" s="12" t="s">
         <v>10</v>
       </c>
       <c r="M20" s="11"/>
     </row>
     <row r="21" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="20"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="37"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="38"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="21"/>
     </row>
     <row r="22" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
       <c r="I22" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
       <c r="L22" s="12" t="s">
         <v>10</v>
       </c>
       <c r="M22" s="11"/>
     </row>
     <row r="23" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="38"/>
+      <c r="A23" s="31"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="21"/>
     </row>
     <row r="24" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
+      <c r="A24" s="31"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
       <c r="I24" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="42"/>
       <c r="L24" s="12" t="s">
         <v>10</v>
       </c>
       <c r="M24" s="11"/>
     </row>
     <row r="25" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="37"/>
-      <c r="L25" s="37"/>
-      <c r="M25" s="38"/>
+      <c r="A25" s="31"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="21"/>
     </row>
     <row r="26" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
+      <c r="A26" s="31"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
       <c r="I26" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
       <c r="L26" s="12" t="s">
         <v>10</v>
       </c>
       <c r="M26" s="11"/>
     </row>
     <row r="27" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="37"/>
-      <c r="L27" s="37"/>
-      <c r="M27" s="38"/>
+      <c r="A27" s="31"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="21"/>
     </row>
     <row r="28" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
+      <c r="A28" s="31"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
       <c r="I28" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J28" s="40"/>
-      <c r="K28" s="40"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="42"/>
       <c r="L28" s="12" t="s">
         <v>10</v>
       </c>
       <c r="M28" s="11"/>
     </row>
     <row r="29" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="32"/>
     </row>
     <row r="30" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="32"/>
     </row>
     <row r="31" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="32"/>
     </row>
     <row r="32" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="B13:M13"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C19:M19"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="A16:M18"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
     <mergeCell ref="C23:M23"/>
     <mergeCell ref="C25:M25"/>
     <mergeCell ref="C27:M27"/>
@@ -1269,6 +1249,26 @@
     <mergeCell ref="J20:K20"/>
     <mergeCell ref="C20:H20"/>
     <mergeCell ref="C22:H22"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B13:M13"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C19:M19"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="A16:M18"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="J28:K28"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">

--- a/在宅評価シート.xlsx
+++ b/在宅評価シート.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Relife-host-pc\nas\作業管理\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\RELIFE-HOST-PC\nas\作業管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4797C8-5343-44F7-9853-4D86300B0E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C087F1D6-1ED9-4C8C-9245-90D5010B1C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="原紙 " sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'原紙 '!$A$1:$M$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'原紙 '!$A$1:$M$28</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>在宅評価シート（面談記録)</t>
     <phoneticPr fontId="1"/>
@@ -89,13 +89,6 @@
     <t>作成年月</t>
     <rPh sb="0" eb="4">
       <t>サクセイネンゲツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>サービス管理責任者</t>
-    <rPh sb="4" eb="9">
-      <t>カンリセキニンシャ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -388,14 +381,59 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -403,15 +441,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -438,42 +467,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -774,42 +767,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="33"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
     </row>
     <row r="3" spans="1:13" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
       <c r="E3" s="2" t="s">
         <v>1</v>
       </c>
@@ -831,87 +824,87 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
     </row>
     <row r="6" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
     </row>
     <row r="7" spans="1:13" ht="54.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>1</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="37"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="21"/>
     </row>
     <row r="8" spans="1:13" ht="54.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>2</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="37"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="21"/>
     </row>
     <row r="9" spans="1:13" ht="54.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>3</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="37"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="21"/>
     </row>
     <row r="10" spans="1:13" ht="31.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="6"/>
@@ -928,311 +921,321 @@
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
       <c r="G11" s="7"/>
       <c r="H11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="39"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="24"/>
     </row>
     <row r="12" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>1</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
     </row>
     <row r="13" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>2</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
     </row>
     <row r="14" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>3</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
     </row>
     <row r="15" spans="1:13" ht="31.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="24"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="36"/>
     </row>
     <row r="17" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="27"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="39"/>
     </row>
     <row r="18" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="30"/>
+      <c r="A18" s="40"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="42"/>
     </row>
     <row r="19" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="21"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="16"/>
     </row>
     <row r="20" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="31"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="10" t="s">
+      <c r="A20" s="27"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="12" t="s">
-        <v>10</v>
-      </c>
       <c r="M20" s="11"/>
     </row>
     <row r="21" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="21"/>
+      <c r="A21" s="27"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="16"/>
     </row>
     <row r="22" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="31"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="10" t="s">
+      <c r="A22" s="27"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="J22" s="42"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="12" t="s">
-        <v>10</v>
-      </c>
       <c r="M22" s="11"/>
     </row>
     <row r="23" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="21"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="16"/>
     </row>
     <row r="24" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="31"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="10" t="s">
+      <c r="A24" s="27"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="J24" s="42"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="12" t="s">
-        <v>10</v>
-      </c>
       <c r="M24" s="11"/>
     </row>
     <row r="25" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="31"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="21"/>
+      <c r="A25" s="27"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="16"/>
     </row>
     <row r="26" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="31"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="10" t="s">
+      <c r="A26" s="27"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="12" t="s">
-        <v>10</v>
-      </c>
       <c r="M26" s="11"/>
     </row>
     <row r="27" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="31"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="21"/>
+      <c r="A27" s="27"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="16"/>
     </row>
     <row r="28" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="31"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="10" t="s">
+      <c r="A28" s="27"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="J28" s="42"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="12" t="s">
-        <v>10</v>
-      </c>
       <c r="M28" s="11"/>
     </row>
     <row r="29" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="32"/>
-      <c r="B29" s="32"/>
+      <c r="A29" s="31"/>
+      <c r="B29" s="31"/>
     </row>
     <row r="30" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="32"/>
-      <c r="B30" s="32"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="31"/>
     </row>
     <row r="31" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="32"/>
-      <c r="B31" s="32"/>
+      <c r="A31" s="31"/>
+      <c r="B31" s="31"/>
     </row>
     <row r="32" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="32"/>
-      <c r="B32" s="32"/>
+      <c r="A32" s="31"/>
+      <c r="B32" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B13:M13"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C19:M19"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="A16:M18"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="C23:M23"/>
     <mergeCell ref="C25:M25"/>
     <mergeCell ref="C27:M27"/>
@@ -1249,26 +1252,6 @@
     <mergeCell ref="J20:K20"/>
     <mergeCell ref="C20:H20"/>
     <mergeCell ref="C22:H22"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="B13:M13"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C19:M19"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="A16:M18"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="J28:K28"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">

--- a/在宅評価シート.xlsx
+++ b/在宅評価シート.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\RELIFE-HOST-PC\nas\作業管理\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Relife-host-pc\nas\作業管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C087F1D6-1ED9-4C8C-9245-90D5010B1C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B139C4CF-721B-4202-B74D-6EBF2CE76E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -381,6 +381,21 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -390,23 +405,44 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -420,53 +456,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -767,42 +767,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
     </row>
     <row r="3" spans="1:13" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
       <c r="E3" s="2" t="s">
         <v>1</v>
       </c>
@@ -824,87 +824,87 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
     </row>
     <row r="6" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
     </row>
     <row r="7" spans="1:13" ht="54.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>1</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="21"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="41"/>
     </row>
     <row r="8" spans="1:13" ht="54.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>2</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="21"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="41"/>
     </row>
     <row r="9" spans="1:13" ht="54.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>3</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="21"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="41"/>
     </row>
     <row r="10" spans="1:13" ht="31.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="6"/>
@@ -921,321 +921,301 @@
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
       <c r="G11" s="7"/>
       <c r="H11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="24"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="36"/>
     </row>
     <row r="12" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>1</v>
       </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
     </row>
     <row r="13" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>2</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
     </row>
     <row r="14" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>3</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
     </row>
     <row r="15" spans="1:13" ht="31.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="36"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="24"/>
     </row>
     <row r="17" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="37"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="39"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="27"/>
     </row>
     <row r="18" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="40"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="41"/>
-      <c r="M18" s="42"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="30"/>
     </row>
     <row r="19" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="16"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="21"/>
     </row>
     <row r="20" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="27"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
       <c r="L20" s="12" t="s">
         <v>9</v>
       </c>
       <c r="M20" s="11"/>
     </row>
     <row r="21" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="27"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="16"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="21"/>
     </row>
     <row r="22" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="27"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
       <c r="L22" s="12" t="s">
         <v>9</v>
       </c>
       <c r="M22" s="11"/>
     </row>
     <row r="23" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="27"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="16"/>
+      <c r="A23" s="31"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="21"/>
     </row>
     <row r="24" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="27"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
+      <c r="A24" s="31"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
       <c r="I24" s="10"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
       <c r="L24" s="12" t="s">
         <v>9</v>
       </c>
       <c r="M24" s="11"/>
     </row>
     <row r="25" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="27"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="16"/>
+      <c r="A25" s="31"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="21"/>
     </row>
     <row r="26" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="27"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
+      <c r="A26" s="31"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
       <c r="I26" s="10"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
       <c r="L26" s="12" t="s">
         <v>9</v>
       </c>
       <c r="M26" s="11"/>
     </row>
     <row r="27" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="27"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="16"/>
+      <c r="A27" s="31"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="21"/>
     </row>
     <row r="28" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
+      <c r="A28" s="31"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
       <c r="I28" s="10"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
       <c r="L28" s="12" t="s">
         <v>9</v>
       </c>
       <c r="M28" s="11"/>
     </row>
     <row r="29" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="31"/>
-      <c r="B29" s="31"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="32"/>
     </row>
     <row r="30" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="31"/>
-      <c r="B30" s="31"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="32"/>
     </row>
     <row r="31" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="31"/>
-      <c r="B31" s="31"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="32"/>
     </row>
     <row r="32" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="31"/>
-      <c r="B32" s="31"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="B13:M13"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C19:M19"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="A16:M18"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
     <mergeCell ref="C23:M23"/>
     <mergeCell ref="C25:M25"/>
     <mergeCell ref="C27:M27"/>
@@ -1252,6 +1232,26 @@
     <mergeCell ref="J20:K20"/>
     <mergeCell ref="C20:H20"/>
     <mergeCell ref="C22:H22"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B13:M13"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C19:M19"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="A16:M18"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="J28:K28"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
